--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/69.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/69.xlsx
@@ -426,13 +426,13 @@
         <v>-12.93478937436983</v>
       </c>
       <c r="E2">
-        <v>-9.643292378087468</v>
+        <v>-7.142850170012203</v>
       </c>
       <c r="F2">
-        <v>-2.602984835636214</v>
+        <v>-1.610675240148658</v>
       </c>
       <c r="G2">
-        <v>-12.6764077645461</v>
+        <v>-10.4193705111461</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.35438998244938</v>
       </c>
       <c r="E3">
-        <v>-11.12306182957391</v>
+        <v>-6.656265637888023</v>
       </c>
       <c r="F3">
-        <v>-2.366934917269272</v>
+        <v>-1.594792951934783</v>
       </c>
       <c r="G3">
-        <v>-12.23638660419387</v>
+        <v>-10.13619306680792</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.71691257387865</v>
       </c>
       <c r="E4">
-        <v>-10.82760607141747</v>
+        <v>-7.227469235319531</v>
       </c>
       <c r="F4">
-        <v>-2.327469837465098</v>
+        <v>-1.781355373291079</v>
       </c>
       <c r="G4">
-        <v>-10.58189843385108</v>
+        <v>-10.15408987599322</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.10794792749142</v>
       </c>
       <c r="E5">
-        <v>-12.88476501582989</v>
+        <v>-8.687897574319214</v>
       </c>
       <c r="F5">
-        <v>-2.592303866344517</v>
+        <v>-1.612979758263246</v>
       </c>
       <c r="G5">
-        <v>-10.91305230414438</v>
+        <v>-8.522312048049837</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.52491552345071</v>
       </c>
       <c r="E6">
-        <v>-13.18194159410925</v>
+        <v>-9.418630254092934</v>
       </c>
       <c r="F6">
-        <v>-2.321015198662485</v>
+        <v>-1.357501310831045</v>
       </c>
       <c r="G6">
-        <v>-11.6582792788531</v>
+        <v>-8.513032588903259</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.994477035575988</v>
       </c>
       <c r="E7">
-        <v>-14.18970819977621</v>
+        <v>-10.41761162018501</v>
       </c>
       <c r="F7">
-        <v>-2.527897472409453</v>
+        <v>-1.384529282449587</v>
       </c>
       <c r="G7">
-        <v>-9.029838542493344</v>
+        <v>-8.98403052386645</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.520031534774533</v>
       </c>
       <c r="E8">
-        <v>-14.71013401815972</v>
+        <v>-10.5912333136391</v>
       </c>
       <c r="F8">
-        <v>-1.820719392272112</v>
+        <v>-1.334283000897978</v>
       </c>
       <c r="G8">
-        <v>-10.28226426763718</v>
+        <v>-7.91761773148318</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.115886361189055</v>
       </c>
       <c r="E9">
-        <v>-15.26397091777181</v>
+        <v>-11.90317751840128</v>
       </c>
       <c r="F9">
-        <v>-1.824277230267136</v>
+        <v>-1.341425184644915</v>
       </c>
       <c r="G9">
-        <v>-9.628795683640446</v>
+        <v>-7.561012387083966</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.787559765448073</v>
       </c>
       <c r="E10">
-        <v>-14.85719621155881</v>
+        <v>-12.20624564136461</v>
       </c>
       <c r="F10">
-        <v>-2.529299070054989</v>
+        <v>-0.940207918201183</v>
       </c>
       <c r="G10">
-        <v>-9.222909558343641</v>
+        <v>-7.213514353463287</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.545518055013547</v>
       </c>
       <c r="E11">
-        <v>-15.64607902606502</v>
+        <v>-13.01474580527206</v>
       </c>
       <c r="F11">
-        <v>-1.714777828393278</v>
+        <v>-1.130009256102425</v>
       </c>
       <c r="G11">
-        <v>-9.674504385901162</v>
+        <v>-6.608012263785048</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.39803161652557</v>
       </c>
       <c r="E12">
-        <v>-14.95647847570297</v>
+        <v>-12.87087618604837</v>
       </c>
       <c r="F12">
-        <v>-1.414191462409032</v>
+        <v>-0.9082387350249417</v>
       </c>
       <c r="G12">
-        <v>-7.814573691027825</v>
+        <v>-6.881324282416198</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.349014434708531</v>
       </c>
       <c r="E13">
-        <v>-15.92752821411574</v>
+        <v>-13.66497580261142</v>
       </c>
       <c r="F13">
-        <v>-1.614657202253915</v>
+        <v>-0.8430967508361914</v>
       </c>
       <c r="G13">
-        <v>-7.883078809871963</v>
+        <v>-5.908752213889109</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.401283416792756</v>
       </c>
       <c r="E14">
-        <v>-16.29710603482974</v>
+        <v>-14.87173261312343</v>
       </c>
       <c r="F14">
-        <v>-1.808864626370648</v>
+        <v>-0.7560717849676866</v>
       </c>
       <c r="G14">
-        <v>-8.160221129692051</v>
+        <v>-5.991793938196188</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.544812154554091</v>
       </c>
       <c r="E15">
-        <v>-17.74655282436082</v>
+        <v>-14.7825669599124</v>
       </c>
       <c r="F15">
-        <v>-0.7693861342328829</v>
+        <v>-0.3254814387880867</v>
       </c>
       <c r="G15">
-        <v>-7.75304389163493</v>
+        <v>-5.125890957489955</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.766729796232724</v>
       </c>
       <c r="E16">
-        <v>-18.2615942871492</v>
+        <v>-16.07982532346771</v>
       </c>
       <c r="F16">
-        <v>-0.5313572461406534</v>
+        <v>-0.1796995446716101</v>
       </c>
       <c r="G16">
-        <v>-6.784368335207563</v>
+        <v>-4.979521807562158</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.039950637442837</v>
       </c>
       <c r="E17">
-        <v>-17.9371789377137</v>
+        <v>-17.09249173801097</v>
       </c>
       <c r="F17">
-        <v>-0.969381361392976</v>
+        <v>0.2885922871116036</v>
       </c>
       <c r="G17">
-        <v>-7.720117205701339</v>
+        <v>-4.197037953354481</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.338028958757393</v>
       </c>
       <c r="E18">
-        <v>-18.68221706687766</v>
+        <v>-17.80678152866284</v>
       </c>
       <c r="F18">
-        <v>0.1500867722613179</v>
+        <v>0.3598534213048339</v>
       </c>
       <c r="G18">
-        <v>-6.45524382932984</v>
+        <v>-4.547598241598985</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.625520181842798</v>
       </c>
       <c r="E19">
-        <v>-20.56706757529822</v>
+        <v>-17.94106889688629</v>
       </c>
       <c r="F19">
-        <v>-0.2061518009452067</v>
+        <v>0.7207134562515769</v>
       </c>
       <c r="G19">
-        <v>-6.59010552296313</v>
+        <v>-4.574771199385324</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.876072530405493</v>
       </c>
       <c r="E20">
-        <v>-22.32567328533296</v>
+        <v>-18.5592644690954</v>
       </c>
       <c r="F20">
-        <v>-0.3755835844116092</v>
+        <v>0.7411542502830575</v>
       </c>
       <c r="G20">
-        <v>-7.101558324416214</v>
+        <v>-4.748141158731416</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.06088037427713</v>
       </c>
       <c r="E21">
-        <v>-22.14866882179515</v>
+        <v>-19.64237129682797</v>
       </c>
       <c r="F21">
-        <v>-0.08088442555905988</v>
+        <v>1.147436983394909</v>
       </c>
       <c r="G21">
-        <v>-6.94995189144529</v>
+        <v>-4.871382837521865</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.16700535136499</v>
       </c>
       <c r="E22">
-        <v>-21.1252065252176</v>
+        <v>-19.79358157241809</v>
       </c>
       <c r="F22">
-        <v>0.6587565447265907</v>
+        <v>1.361636226410805</v>
       </c>
       <c r="G22">
-        <v>-7.90053531650054</v>
+        <v>-4.723434557371835</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.18352894022906</v>
       </c>
       <c r="E23">
-        <v>-21.66209334661899</v>
+        <v>-20.02314350528892</v>
       </c>
       <c r="F23">
-        <v>0.4621261459566692</v>
+        <v>1.808136196928572</v>
       </c>
       <c r="G23">
-        <v>-6.950620621644223</v>
+        <v>-5.677374875603906</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.11777352428505</v>
       </c>
       <c r="E24">
-        <v>-22.1253200098116</v>
+        <v>-20.41839777362641</v>
       </c>
       <c r="F24">
-        <v>0.5818683107661434</v>
+        <v>1.817263148972617</v>
       </c>
       <c r="G24">
-        <v>-7.668154882916938</v>
+        <v>-5.379823042534212</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.977756504273776</v>
       </c>
       <c r="E25">
-        <v>-24.21411940211562</v>
+        <v>-20.55761665004422</v>
       </c>
       <c r="F25">
-        <v>0.3866577337246203</v>
+        <v>1.641727126114985</v>
       </c>
       <c r="G25">
-        <v>-7.186026893850718</v>
+        <v>-5.22252909232682</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.786729486486294</v>
       </c>
       <c r="E26">
-        <v>-23.0427163881815</v>
+        <v>-21.14797116405416</v>
       </c>
       <c r="F26">
-        <v>0.5756041964661736</v>
+        <v>1.526637072639633</v>
       </c>
       <c r="G26">
-        <v>-7.676212750759524</v>
+        <v>-5.121749465020327</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.565478807543636</v>
       </c>
       <c r="E27">
-        <v>-22.59849120192506</v>
+        <v>-21.38399975780795</v>
       </c>
       <c r="F27">
-        <v>0.2898398084202197</v>
+        <v>1.593226214681074</v>
       </c>
       <c r="G27">
-        <v>-7.845610055458492</v>
+        <v>-5.533213859550803</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.344338015784924</v>
       </c>
       <c r="E28">
-        <v>-22.61305024585972</v>
+        <v>-20.14245973844302</v>
       </c>
       <c r="F28">
-        <v>0.6272835536246263</v>
+        <v>1.641196970977193</v>
       </c>
       <c r="G28">
-        <v>-6.283045803104649</v>
+        <v>-5.378535240319436</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.145435938225186</v>
       </c>
       <c r="E29">
-        <v>-22.78440317383596</v>
+        <v>-20.45752831752669</v>
       </c>
       <c r="F29">
-        <v>0.3941486601481362</v>
+        <v>1.712413373330672</v>
       </c>
       <c r="G29">
-        <v>-7.859262745262446</v>
+        <v>-5.649152474881619</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.990251698968079</v>
       </c>
       <c r="E30">
-        <v>-22.66125132319737</v>
+        <v>-19.81982407929254</v>
       </c>
       <c r="F30">
-        <v>0.2677646455030157</v>
+        <v>1.307638268891916</v>
       </c>
       <c r="G30">
-        <v>-6.982497864641865</v>
+        <v>-5.174214990726696</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.888737540265833</v>
       </c>
       <c r="E31">
-        <v>-22.2941686916616</v>
+        <v>-19.54886283704358</v>
       </c>
       <c r="F31">
-        <v>-0.1852744572924508</v>
+        <v>1.559718753237834</v>
       </c>
       <c r="G31">
-        <v>-7.181594073373634</v>
+        <v>-5.61644428495362</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.843344344617122</v>
       </c>
       <c r="E32">
-        <v>-21.77286434932061</v>
+        <v>-20.21433114941876</v>
       </c>
       <c r="F32">
-        <v>0.2347467491948302</v>
+        <v>1.278155016291476</v>
       </c>
       <c r="G32">
-        <v>-7.076573637231334</v>
+        <v>-5.343913555069737</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.847313685238348</v>
       </c>
       <c r="E33">
-        <v>-20.18015475608287</v>
+        <v>-18.70459678542356</v>
       </c>
       <c r="F33">
-        <v>0.5318075835127608</v>
+        <v>1.297074927771417</v>
       </c>
       <c r="G33">
-        <v>-7.311291315965661</v>
+        <v>-4.904276418000063</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.884837246943729</v>
       </c>
       <c r="E34">
-        <v>-20.34608257219792</v>
+        <v>-18.3717630028078</v>
       </c>
       <c r="F34">
-        <v>0.5650574226937302</v>
+        <v>1.273777922935084</v>
       </c>
       <c r="G34">
-        <v>-5.881658709195714</v>
+        <v>-4.588910539383551</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.939651413085096</v>
       </c>
       <c r="E35">
-        <v>-20.76765180299398</v>
+        <v>-18.4403059853879</v>
       </c>
       <c r="F35">
-        <v>0.2411061257461219</v>
+        <v>1.253487891770912</v>
       </c>
       <c r="G35">
-        <v>-7.695973397083434</v>
+        <v>-4.560638480478175</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.989284557370858</v>
       </c>
       <c r="E36">
-        <v>-20.42985934133982</v>
+        <v>-17.36463944044993</v>
       </c>
       <c r="F36">
-        <v>0.2117993154024782</v>
+        <v>1.885608429907993</v>
       </c>
       <c r="G36">
-        <v>-6.405085753864341</v>
+        <v>-5.019225180214637</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.019415745538916</v>
       </c>
       <c r="E37">
-        <v>-20.17606101557994</v>
+        <v>-17.58011781915691</v>
       </c>
       <c r="F37">
-        <v>-0.1160701593603717</v>
+        <v>1.04046161699738</v>
       </c>
       <c r="G37">
-        <v>-6.466943297265623</v>
+        <v>-4.424406220991626</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.012624310569676</v>
       </c>
       <c r="E38">
-        <v>-20.38429383587464</v>
+        <v>-17.07169245689374</v>
       </c>
       <c r="F38">
-        <v>0.1568271978178974</v>
+        <v>1.059373244803293</v>
       </c>
       <c r="G38">
-        <v>-6.377820100802905</v>
+        <v>-4.266572651861333</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.964490628831031</v>
       </c>
       <c r="E39">
-        <v>-18.65035019528568</v>
+        <v>-16.46602717226386</v>
       </c>
       <c r="F39">
-        <v>0.1064608029928819</v>
+        <v>1.24742424238242</v>
       </c>
       <c r="G39">
-        <v>-7.622899725395102</v>
+        <v>-4.22811073378608</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.868630844549839</v>
       </c>
       <c r="E40">
-        <v>-17.49617802495073</v>
+        <v>-16.17240091760651</v>
       </c>
       <c r="F40">
-        <v>-0.481209540309977</v>
+        <v>1.117715160982462</v>
       </c>
       <c r="G40">
-        <v>-5.69162015305939</v>
+        <v>-4.411485161751851</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.731938165111861</v>
       </c>
       <c r="E41">
-        <v>-18.94751318814301</v>
+        <v>-15.46459137325962</v>
       </c>
       <c r="F41">
-        <v>-0.03051885910144714</v>
+        <v>0.9086683632119792</v>
       </c>
       <c r="G41">
-        <v>-6.101684186826756</v>
+        <v>-4.561939524875108</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.557895214740627</v>
       </c>
       <c r="E42">
-        <v>-19.28600303479435</v>
+        <v>-15.26978547839766</v>
       </c>
       <c r="F42">
-        <v>-0.2902426894729958</v>
+        <v>0.9054493274847003</v>
       </c>
       <c r="G42">
-        <v>-6.419592564417428</v>
+        <v>-4.155384669379371</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.361526985646087</v>
       </c>
       <c r="E43">
-        <v>-16.77082064382412</v>
+        <v>-14.59162385337898</v>
       </c>
       <c r="F43">
-        <v>-0.1248599658714772</v>
+        <v>1.050821179736791</v>
       </c>
       <c r="G43">
-        <v>-6.045726035576454</v>
+        <v>-4.705603959097321</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.152729149072483</v>
       </c>
       <c r="E44">
-        <v>-17.82558828121669</v>
+        <v>-13.98452304248867</v>
       </c>
       <c r="F44">
-        <v>-0.3865486837224663</v>
+        <v>1.263529361427648</v>
       </c>
       <c r="G44">
-        <v>-6.692374895762295</v>
+        <v>-4.007042434310168</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.949439219095023</v>
       </c>
       <c r="E45">
-        <v>-17.3879973093815</v>
+        <v>-14.38575489651628</v>
       </c>
       <c r="F45">
-        <v>-0.1305839846248218</v>
+        <v>0.7588448645372438</v>
       </c>
       <c r="G45">
-        <v>-6.292308709523529</v>
+        <v>-3.935369123384947</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.760980855417621</v>
       </c>
       <c r="E46">
-        <v>-16.41346970293084</v>
+        <v>-12.95003391170245</v>
       </c>
       <c r="F46">
-        <v>-0.5228697937315697</v>
+        <v>0.8659577399236367</v>
       </c>
       <c r="G46">
-        <v>-6.405837247701756</v>
+        <v>-4.469793800335034</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.599932025021867</v>
       </c>
       <c r="E47">
-        <v>-15.28576193469672</v>
+        <v>-12.52434829803342</v>
       </c>
       <c r="F47">
-        <v>0.04245036867635571</v>
+        <v>0.8365672644723102</v>
       </c>
       <c r="G47">
-        <v>-6.768921329721324</v>
+        <v>-4.803622591424062</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.469770539926563</v>
       </c>
       <c r="E48">
-        <v>-14.11324944463071</v>
+        <v>-12.65471853624024</v>
       </c>
       <c r="F48">
-        <v>-0.2366721695339517</v>
+        <v>0.7208062334006905</v>
       </c>
       <c r="G48">
-        <v>-7.108768692600747</v>
+        <v>-4.646550447767801</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.374696020069212</v>
       </c>
       <c r="E49">
-        <v>-14.42184683435741</v>
+        <v>-11.74427789394613</v>
       </c>
       <c r="F49">
-        <v>-0.1921002046915187</v>
+        <v>0.7945276187802353</v>
       </c>
       <c r="G49">
-        <v>-7.186295048039399</v>
+        <v>-4.879007023898806</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.311837629901018</v>
       </c>
       <c r="E50">
-        <v>-14.55027435721494</v>
+        <v>-11.05950469687626</v>
       </c>
       <c r="F50">
-        <v>-0.3425217846310754</v>
+        <v>0.7615619096184262</v>
       </c>
       <c r="G50">
-        <v>-5.988728373026822</v>
+        <v>-5.411614211347834</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.277811152601723</v>
       </c>
       <c r="E51">
-        <v>-13.02747081723361</v>
+        <v>-12.00707882603326</v>
       </c>
       <c r="F51">
-        <v>-0.5693817950313591</v>
+        <v>0.6758333387353025</v>
       </c>
       <c r="G51">
-        <v>-7.168586939949837</v>
+        <v>-5.143910256860208</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.266174833288461</v>
       </c>
       <c r="E52">
-        <v>-13.69244552594195</v>
+        <v>-10.87446672044884</v>
       </c>
       <c r="F52">
-        <v>-0.07224289681305543</v>
+        <v>0.4688466906955817</v>
       </c>
       <c r="G52">
-        <v>-6.380044787405295</v>
+        <v>-4.596514862487257</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.2695857865933</v>
       </c>
       <c r="E53">
-        <v>-13.42438703553191</v>
+        <v>-10.59928494042473</v>
       </c>
       <c r="F53">
-        <v>-0.1811317919110504</v>
+        <v>0.5215813879252009</v>
       </c>
       <c r="G53">
-        <v>-7.469406281466792</v>
+        <v>-4.710487013767746</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.282406195947251</v>
       </c>
       <c r="E54">
-        <v>-12.82760208843107</v>
+        <v>-10.63898607204998</v>
       </c>
       <c r="F54">
-        <v>0.1286759600011591</v>
+        <v>0.4869034433418052</v>
       </c>
       <c r="G54">
-        <v>-7.373152169912482</v>
+        <v>-4.993935922840144</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.298916338323733</v>
       </c>
       <c r="E55">
-        <v>-12.47049115666019</v>
+        <v>-10.03201205843188</v>
       </c>
       <c r="F55">
-        <v>-0.4897665755808959</v>
+        <v>0.4222212030616087</v>
       </c>
       <c r="G55">
-        <v>-7.765686865049407</v>
+        <v>-5.728307618725593</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.317636349102028</v>
       </c>
       <c r="E56">
-        <v>-12.66712655502126</v>
+        <v>-9.019105634766216</v>
       </c>
       <c r="F56">
-        <v>-0.07760077717436265</v>
+        <v>0.6506277754029192</v>
       </c>
       <c r="G56">
-        <v>-7.535534428613735</v>
+        <v>-5.546982418448632</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.336714954235849</v>
       </c>
       <c r="E57">
-        <v>-13.78230856415016</v>
+        <v>-9.351491098455213</v>
       </c>
       <c r="F57">
-        <v>-0.388685871621689</v>
+        <v>0.5446141435600412</v>
       </c>
       <c r="G57">
-        <v>-8.212633686669792</v>
+        <v>-5.620986353433501</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.360456702168441</v>
       </c>
       <c r="E58">
-        <v>-12.48229235992418</v>
+        <v>-8.61170599914016</v>
       </c>
       <c r="F58">
-        <v>-0.2724460441912511</v>
+        <v>0.5336639548624346</v>
       </c>
       <c r="G58">
-        <v>-8.052211270927788</v>
+        <v>-5.639465818633712</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.390238319245718</v>
       </c>
       <c r="E59">
-        <v>-12.1142542203728</v>
+        <v>-8.472260699021966</v>
       </c>
       <c r="F59">
-        <v>-0.04071854693211745</v>
+        <v>0.4458379577154226</v>
       </c>
       <c r="G59">
-        <v>-8.749557825502029</v>
+        <v>-6.183699642016659</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.432912771377087</v>
       </c>
       <c r="E60">
-        <v>-12.23567619394046</v>
+        <v>-8.497140135220107</v>
       </c>
       <c r="F60">
-        <v>-0.4111685913010704</v>
+        <v>0.409192640550378</v>
       </c>
       <c r="G60">
-        <v>-8.694205504085414</v>
+        <v>-5.825902501223308</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.488759944025486</v>
       </c>
       <c r="E61">
-        <v>-10.28324726790343</v>
+        <v>-8.116358869811137</v>
       </c>
       <c r="F61">
-        <v>-0.2541374678545765</v>
+        <v>0.426355584768981</v>
       </c>
       <c r="G61">
-        <v>-8.413620216904485</v>
+        <v>-6.211650578004726</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.562677273048307</v>
       </c>
       <c r="E62">
-        <v>-10.9910477553023</v>
+        <v>-9.057380297079046</v>
       </c>
       <c r="F62">
-        <v>-0.6116293609415367</v>
+        <v>-0.007156413240292681</v>
       </c>
       <c r="G62">
-        <v>-8.580786213909983</v>
+        <v>-6.612216656619922</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.650418452104646</v>
       </c>
       <c r="E63">
-        <v>-11.44272680977536</v>
+        <v>-7.774028877201297</v>
       </c>
       <c r="F63">
-        <v>-0.6364621589426603</v>
+        <v>0.7028488848428027</v>
       </c>
       <c r="G63">
-        <v>-9.06478797175143</v>
+        <v>-6.75603999702802</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.752491744339761</v>
       </c>
       <c r="E64">
-        <v>-11.71406844384096</v>
+        <v>-7.023379968741843</v>
       </c>
       <c r="F64">
-        <v>-0.3990512329329192</v>
+        <v>0.06368805214932943</v>
       </c>
       <c r="G64">
-        <v>-9.029222781023041</v>
+        <v>-6.948200612855016</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.860171616153075</v>
       </c>
       <c r="E65">
-        <v>-11.19494229749766</v>
+        <v>-8.231200970645657</v>
       </c>
       <c r="F65">
-        <v>-0.1561457459404089</v>
+        <v>0.3373930675453281</v>
       </c>
       <c r="G65">
-        <v>-9.618625687743805</v>
+        <v>-7.506788961696243</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.970697654842968</v>
       </c>
       <c r="E66">
-        <v>-11.58547336744514</v>
+        <v>-8.767046243025275</v>
       </c>
       <c r="F66">
-        <v>-0.8068788712509913</v>
+        <v>0.01996102205775193</v>
       </c>
       <c r="G66">
-        <v>-8.127095811026104</v>
+        <v>-7.068029119194476</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.073909429921985</v>
       </c>
       <c r="E67">
-        <v>-11.58387934459445</v>
+        <v>-8.04279833803054</v>
       </c>
       <c r="F67">
-        <v>-0.6105176918869798</v>
+        <v>-0.07839766661585576</v>
       </c>
       <c r="G67">
-        <v>-8.637297226265343</v>
+        <v>-7.003897231007714</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.165687088697961</v>
       </c>
       <c r="E68">
-        <v>-10.35527717546943</v>
+        <v>-7.72465039662166</v>
       </c>
       <c r="F68">
-        <v>-0.5163720798240103</v>
+        <v>0.6327789429747982</v>
       </c>
       <c r="G68">
-        <v>-8.707801914615201</v>
+        <v>-7.182127071205457</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.236474510570265</v>
       </c>
       <c r="E69">
-        <v>-11.01701855373629</v>
+        <v>-8.479977218731037</v>
       </c>
       <c r="F69">
-        <v>-0.7083006652156418</v>
+        <v>0.1927253275856168</v>
       </c>
       <c r="G69">
-        <v>-9.259967805110243</v>
+        <v>-7.117442321913637</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.281930198325062</v>
       </c>
       <c r="E70">
-        <v>-10.02741112884009</v>
+        <v>-7.278215315049485</v>
       </c>
       <c r="F70">
-        <v>-0.6934579780922803</v>
+        <v>0.2869819408805614</v>
       </c>
       <c r="G70">
-        <v>-8.408879515692249</v>
+        <v>-7.232480468857772</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.295255721342778</v>
       </c>
       <c r="E71">
-        <v>-12.16677546191376</v>
+        <v>-7.54509640221753</v>
       </c>
       <c r="F71">
-        <v>-0.635946914418119</v>
+        <v>-0.161760420196584</v>
       </c>
       <c r="G71">
-        <v>-8.125913946268582</v>
+        <v>-7.569772090580877</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.272956888060261</v>
       </c>
       <c r="E72">
-        <v>-10.63227940204462</v>
+        <v>-8.290084718167396</v>
       </c>
       <c r="F72">
-        <v>-0.5464998022638284</v>
+        <v>-0.03732141221323668</v>
       </c>
       <c r="G72">
-        <v>-8.573069332257942</v>
+        <v>-7.182362119938745</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.212522828454357</v>
       </c>
       <c r="E73">
-        <v>-10.58417342266114</v>
+        <v>-8.405103429488214</v>
       </c>
       <c r="F73">
-        <v>-0.9222721071957681</v>
+        <v>-0.003502484626544062</v>
       </c>
       <c r="G73">
-        <v>-9.304848870986142</v>
+        <v>-7.153106829008205</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.111991926846869</v>
       </c>
       <c r="E74">
-        <v>-13.3997611938782</v>
+        <v>-8.956046634209406</v>
       </c>
       <c r="F74">
-        <v>-0.9898975368581113</v>
+        <v>0.0443117102304462</v>
       </c>
       <c r="G74">
-        <v>-8.889557485812269</v>
+        <v>-7.230689463721026</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.974386529146863</v>
       </c>
       <c r="E75">
-        <v>-10.96109189974156</v>
+        <v>-8.382773524156393</v>
       </c>
       <c r="F75">
-        <v>-0.419366943486577</v>
+        <v>0.1310169262814705</v>
       </c>
       <c r="G75">
-        <v>-8.046954124611426</v>
+        <v>-6.890441524831351</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.800250522703994</v>
       </c>
       <c r="E76">
-        <v>-12.63494269024874</v>
+        <v>-9.856873326185232</v>
       </c>
       <c r="F76">
-        <v>-0.7340985112410269</v>
+        <v>-0.17526695069923</v>
       </c>
       <c r="G76">
-        <v>-9.778945476574091</v>
+        <v>-6.688829301489736</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.597228609382012</v>
       </c>
       <c r="E77">
-        <v>-13.46644750211515</v>
+        <v>-10.03560313831997</v>
       </c>
       <c r="F77">
-        <v>-0.7181839166984427</v>
+        <v>-0.2633000396969418</v>
       </c>
       <c r="G77">
-        <v>-8.51002992409914</v>
+        <v>-6.646583429863096</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.367665726302453</v>
       </c>
       <c r="E78">
-        <v>-12.37950958537209</v>
+        <v>-10.52480512842058</v>
       </c>
       <c r="F78">
-        <v>-0.7952419659764639</v>
+        <v>-0.2777583643454044</v>
       </c>
       <c r="G78">
-        <v>-9.17503575930024</v>
+        <v>-6.060481137044986</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.121610974973581</v>
       </c>
       <c r="E79">
-        <v>-13.87029228564519</v>
+        <v>-10.44368204504717</v>
       </c>
       <c r="F79">
-        <v>-1.386525647890334</v>
+        <v>0.01004960608325585</v>
       </c>
       <c r="G79">
-        <v>-8.754967256913197</v>
+        <v>-6.465009938670689</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.861646932695015</v>
       </c>
       <c r="E80">
-        <v>-14.55958489977471</v>
+        <v>-11.21824129626713</v>
       </c>
       <c r="F80">
-        <v>-1.480865097925559</v>
+        <v>-0.3519519191445449</v>
       </c>
       <c r="G80">
-        <v>-7.615139806651049</v>
+        <v>-6.911797854105189</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.597294195326169</v>
       </c>
       <c r="E81">
-        <v>-13.80486036470836</v>
+        <v>-12.28150435089809</v>
       </c>
       <c r="F81">
-        <v>-1.433019425107262</v>
+        <v>-0.5683695300651381</v>
       </c>
       <c r="G81">
-        <v>-8.336504369112703</v>
+        <v>-6.760618481508831</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.328986072859551</v>
       </c>
       <c r="E82">
-        <v>-16.94746282944132</v>
+        <v>-12.43416373817066</v>
       </c>
       <c r="F82">
-        <v>-1.309457658203479</v>
+        <v>-0.5802739980107698</v>
       </c>
       <c r="G82">
-        <v>-8.828580547524432</v>
+        <v>-7.017420809535636</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.063125811435617</v>
       </c>
       <c r="E83">
-        <v>-16.63703140774151</v>
+        <v>-13.81166213266788</v>
       </c>
       <c r="F83">
-        <v>-1.494367486591191</v>
+        <v>-0.4320649874040907</v>
       </c>
       <c r="G83">
-        <v>-9.058335718495391</v>
+        <v>-6.499578655191759</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.798795055948628</v>
       </c>
       <c r="E84">
-        <v>-17.21762706026492</v>
+        <v>-14.17840965712708</v>
       </c>
       <c r="F84">
-        <v>-1.277183635823008</v>
+        <v>-0.646371089814948</v>
       </c>
       <c r="G84">
-        <v>-7.972205316880222</v>
+        <v>-6.496890492213871</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.540886624157038</v>
       </c>
       <c r="E85">
-        <v>-16.84139238275965</v>
+        <v>-15.20813483325723</v>
       </c>
       <c r="F85">
-        <v>-1.796213799395094</v>
+        <v>-0.979437741662962</v>
       </c>
       <c r="G85">
-        <v>-7.612723108407382</v>
+        <v>-6.236817345194265</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.290003961926158</v>
       </c>
       <c r="E86">
-        <v>-18.10883527344846</v>
+        <v>-16.45404935851357</v>
       </c>
       <c r="F86">
-        <v>-1.499444550402949</v>
+        <v>-0.9305905726546807</v>
       </c>
       <c r="G86">
-        <v>-7.748104557690337</v>
+        <v>-6.880612515125255</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.052447601227489</v>
       </c>
       <c r="E87">
-        <v>-20.18042646452333</v>
+        <v>-17.69755020712382</v>
       </c>
       <c r="F87">
-        <v>-1.449929717268011</v>
+        <v>-0.7700761642794149</v>
       </c>
       <c r="G87">
-        <v>-7.546108311066167</v>
+        <v>-6.233774953843676</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.832628024142966</v>
       </c>
       <c r="E88">
-        <v>-20.25729278232953</v>
+        <v>-18.85566667831944</v>
       </c>
       <c r="F88">
-        <v>-2.029525963495783</v>
+        <v>-0.7609036520282161</v>
       </c>
       <c r="G88">
-        <v>-7.302376016828404</v>
+        <v>-6.053300563770307</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.640265983642178</v>
       </c>
       <c r="E89">
-        <v>-22.2624059749718</v>
+        <v>-20.2419865401836</v>
       </c>
       <c r="F89">
-        <v>-2.478051292313395</v>
+        <v>-1.079418373711251</v>
       </c>
       <c r="G89">
-        <v>-7.495874093053266</v>
+        <v>-6.16712042995599</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.484133172662948</v>
       </c>
       <c r="E90">
-        <v>-24.41567272324902</v>
+        <v>-21.75782981561515</v>
       </c>
       <c r="F90">
-        <v>-1.901266525050725</v>
+        <v>-1.19490687190735</v>
       </c>
       <c r="G90">
-        <v>-7.308649500625323</v>
+        <v>-5.385702571411958</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.376852330831172</v>
       </c>
       <c r="E91">
-        <v>-25.79206164161435</v>
+        <v>-24.39140915951592</v>
       </c>
       <c r="F91">
-        <v>-1.609804626008316</v>
+        <v>-0.9636689397832706</v>
       </c>
       <c r="G91">
-        <v>-8.384811849621746</v>
+        <v>-5.999666415488575</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.328948871022583</v>
       </c>
       <c r="E92">
-        <v>-28.1253533455925</v>
+        <v>-25.98326287116621</v>
       </c>
       <c r="F92">
-        <v>-1.421616947807727</v>
+        <v>-1.056489164001761</v>
       </c>
       <c r="G92">
-        <v>-8.09326534616029</v>
+        <v>-6.015368332981337</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.353566315139727</v>
       </c>
       <c r="E93">
-        <v>-30.9294523782521</v>
+        <v>-27.26614332974716</v>
       </c>
       <c r="F93">
-        <v>-2.674771154762819</v>
+        <v>-1.265885532816226</v>
       </c>
       <c r="G93">
-        <v>-8.385811634374607</v>
+        <v>-6.646209338217158</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.458678770485438</v>
       </c>
       <c r="E94">
-        <v>-32.39841915499324</v>
+        <v>-30.08775849986843</v>
       </c>
       <c r="F94">
-        <v>-2.553739221907186</v>
+        <v>-1.051678006126301</v>
       </c>
       <c r="G94">
-        <v>-7.058905255688244</v>
+        <v>-5.824548488097746</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.649694105819083</v>
       </c>
       <c r="E95">
-        <v>-33.40959343735098</v>
+        <v>-31.11859768060447</v>
       </c>
       <c r="F95">
-        <v>-1.997187328457893</v>
+        <v>-1.207889874211426</v>
       </c>
       <c r="G95">
-        <v>-8.474305827184866</v>
+        <v>-6.237052393927554</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.931484411154493</v>
       </c>
       <c r="E96">
-        <v>-37.43579627893458</v>
+        <v>-34.68331279301441</v>
       </c>
       <c r="F96">
-        <v>-2.211266458200384</v>
+        <v>-1.121101821420122</v>
       </c>
       <c r="G96">
-        <v>-7.953881447320356</v>
+        <v>-6.892997265987669</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.292499337304659</v>
       </c>
       <c r="E97">
-        <v>-40.11439771141961</v>
+        <v>-36.59965430968432</v>
       </c>
       <c r="F97">
-        <v>-2.221859620547384</v>
+        <v>-1.511942129408985</v>
       </c>
       <c r="G97">
-        <v>-8.847348030186561</v>
+        <v>-6.431225821442426</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.739275789411246</v>
       </c>
       <c r="E98">
-        <v>-41.01972344232206</v>
+        <v>-38.86664236147916</v>
       </c>
       <c r="F98">
-        <v>-2.693914725441516</v>
+        <v>-1.523636192034306</v>
       </c>
       <c r="G98">
-        <v>-7.997891839719427</v>
+        <v>-6.849235164504043</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.236742015618203</v>
       </c>
       <c r="E99">
-        <v>-43.3630479804642</v>
+        <v>-41.85488046847566</v>
       </c>
       <c r="F99">
-        <v>-2.995616902317332</v>
+        <v>-1.357934546982709</v>
       </c>
       <c r="G99">
-        <v>-7.758502981229189</v>
+        <v>-6.67540834987353</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.806940137523112</v>
       </c>
       <c r="E100">
-        <v>-44.79351367119213</v>
+        <v>-44.22432750893104</v>
       </c>
       <c r="F100">
-        <v>-3.255831126191338</v>
+        <v>-1.742238207796081</v>
       </c>
       <c r="G100">
-        <v>-9.671624211281996</v>
+        <v>-7.136381952943808</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.373548426041444</v>
       </c>
       <c r="E101">
-        <v>-48.46101495450966</v>
+        <v>-46.19157360192117</v>
       </c>
       <c r="F101">
-        <v>-2.907739546391346</v>
+        <v>-1.864734694219864</v>
       </c>
       <c r="G101">
-        <v>-8.782143525245075</v>
+        <v>-7.254747198154909</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.01713626954656</v>
       </c>
       <c r="E102">
-        <v>-49.86760766238766</v>
+        <v>-48.36511206409373</v>
       </c>
       <c r="F102">
-        <v>-3.249238150032457</v>
+        <v>-2.03833399408975</v>
       </c>
       <c r="G102">
-        <v>-9.197928181704301</v>
+        <v>-7.245623334648678</v>
       </c>
     </row>
   </sheetData>
